--- a/plan/schedule.xlsx
+++ b/plan/schedule.xlsx
@@ -536,7 +536,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1086,11 +1085,10 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Labs 1 to 11 go with Meetings 1 to 11. Ten are graded, 1 point each; Lab 7 is optional and ungraded (its methods are graded in A3). Notebooks are expected soon after their meeting. AI roles: tool (Lab 2), decision-maker (Lab 5), analyst (Lab 7, optional), source of data (Lab 9), intervention (Lab 10).</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>Labs 1 to 11 go with Meetings 1 to 11. Ten are graded, 1 point each; Lab 7 is optional and ungraded (its methods are graded in A3). Notebooks are expected soon after their meeting. AI roles: tool (Lab 2), decision-maker (Lab 5), analyst (Lab 7, optional), source of data (Lab 9), intervention (Lab 10). Each block of labs works in one semi-synthetic world with a planted truth: Labs 1 to 7 in Houtan Coffee's loyalty program (built on the Starbucks rewards data from Kaggle), Labs 8 and 9 in Airbnb listings and reviews (Inside Airbnb; the city is chosen later), Labs 10 and 11 in real store panels with planted rollouts. Notebooks describe their source data.</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1124,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Review; simulation from scratch</t>
+          <t>Review; semi-synthetic</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Simulated</t>
+          <t>Houtan Coffee world, simulated from scratch</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1153,12 +1151,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Real data and simulation; LLM lab</t>
+          <t>Semi-synthetic; LLM lab</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Email experiment (Hillstrom)</t>
+          <t>Houtan Coffee RCT (randomization, effects and pre-period spend planted)</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -1180,12 +1178,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>From scratch; simulation</t>
+          <t>Semi-synthetic</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Three simulated worlds with known CATE (no heterogeneity, strong heterogeneity, 10% treated)</t>
+          <t>Houtan Coffee RCT, three versions with different planted CATE (no heterogeneity, strong heterogeneity, 10% treated)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1207,12 +1205,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Real data</t>
+          <t>Semi-synthetic</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Coupon RCT</t>
+          <t>Houtan Coffee RCT</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -1234,12 +1232,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Real data; LLM lab</t>
+          <t>Semi-synthetic; LLM lab</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Coupon RCT holdout, with text profiles generated from the features</t>
+          <t>Houtan Coffee RCT holdout, with text profiles generated from the features</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1261,12 +1259,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>From scratch (optimization); real data</t>
+          <t>From scratch (optimization); semi-synthetic</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Coupon RCT with customer-specific costs and three coupon depths</t>
+          <t>Houtan Coffee RCT with customer-specific costs and three coupon depths</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -1293,7 +1291,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Logs built from the coupon RCT by a known targeting rule, with a post-treatment variable and a collider among the columns</t>
+          <t>Logs built from the Houtan Coffee RCT by a known targeting rule (overlap dial), with a post-treatment variable and a collider among the columns; truth from the RCT version</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1315,12 +1313,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Real data; from scratch (in class)</t>
+          <t>Semi-synthetic on real listings; from scratch (in class)</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Orange-juice scanner data (Dominick's)</t>
+          <t>Airbnb listings and host prices; demand with a planted heterogeneous elasticity, confounded by a latent quality carried in the review text</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
@@ -1330,7 +1328,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Naive, fixed-effects and DML elasticities; hand-code partialling-out with cross-fitting, then match DoubleML; stability across learners and splits; sensitivity bounds (how much hidden confounding flips the pricing decision)</t>
+          <t>Naive, fixed-effects and DML elasticities; hand-code partialling-out with cross-fitting, then match DoubleML; stability across learners and splits; the optimal price; sensitivity bounds (how much hidden confounding flips the pricing decision)</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1345,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Public hotel reviews; treatment and bookings simulated from a quality variable carried in the text; gold labels on a subsample</t>
+          <t>Airbnb reviews; the latent quality is planted, with gold labels on a subsample</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1357,7 +1355,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Compare LLM labels with gold, including error by treatment arm; use the label as an outcome with and without PPI; embeddings as DML controls vs the truth; a leakage demo with post-treatment text</t>
+          <t>Compare LLM labels with gold quality, including error by treatment arm; use the label as an outcome with and without PPI; embeddings as DML controls vs the truth; a leakage demo with post-treatment text; a simulator with a confounding dial</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1496,7 +1494,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>On a second email campaign: hand-code the ATE with a robust SE, and CUPED. Have an LLM generate the full readout (SRM, ATE, CUPED, test against the break-even, MDE for a follow-up) and verify it with a simulation test suite. One-page decision memo</t>
+          <t>On the Hillstrom email RCT (resampled, with course-specific costs): hand-code the ATE with a robust SE, and CUPED on history. Have an LLM generate the full readout (SRM, ATE, CUPED, test against the break-even, MDE for a follow-up) and verify it with a simulation test suite. One-page decision memo</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -1508,7 +1506,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>A2: Coupon whom, and at what budget?</t>
+          <t>A2: Email whom, and at what budget?</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -1528,7 +1526,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>CATE from two meta-learners and a causal forest; ranking evaluated with Qini and RATE; a budgeted allocation and a depth-2 policy tree. Frozen policies are submitted and scored by an autograder on a locked RCT set. Memo on value, cost, and what could overturn the recommendation</t>
+          <t>Hillstrom, three arms (men's email, women's email, no email). CATE from two meta-learners and a causal forest; ranking evaluated with Qini and RATE; a budgeted allocation and a depth-2 policy tree. Frozen policies are scored by IPW on a locked holdout of at least 20,000 rows, with paired comparisons. Memo on value, cost, and what could overturn the recommendation</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -1540,7 +1538,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>A3: Learn the policy from the logs</t>
+          <t>A3: Promote and price from the logs</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -1560,7 +1558,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>The same decision, from observational logs only. (1) DAG and adjustment set; regression, IPW and AIPW estimates; overlap and trimming (the methods of Lab 7). (2) DML on the same logs, compared with (1) and with the locked RCT. (3) Generative AI for evaluation: a simulator fitted to the coupon logs, with a planted effect and a dial for hidden confounding, as a testbed for each estimator's bias and coverage and for whether the policy ranking holds as confounding grows. An LLM-coded feature is to be decided (depends on the problem and data). The submitted policy is scored on the locked RCT set next to an RCT-trained benchmark. Memo with a sensitivity bound: how strong hidden confounding must be to change the chosen policy</t>
+          <t>dunnhumby "Breakfast at the Frat" (real grocery data, no experiment). (1) The effect of an in-store display: DAG and adjustment set; regression, IPW and AIPW estimates; overlap and trimming (the methods of Lab 7). (2) The price elasticity by DML, and a recommended price. (3) Generative AI for evaluation: a student-built simulator of the data with a planted elasticity and a dial for hidden confounding, as a testbed for each estimator's bias and coverage. The pipeline is then run on the instructor's locked simulator across several planted-elasticity scenarios. Memo with a sensitivity bound: how strong hidden confounding must be to change the recommended price</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -1592,12 +1590,19 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Panel data. Evaluate the rollout of an AI store assistant: before-after, 2x2 DiD and TWFE with store and period effects; an event study; what the pre-period can and cannot rule out (breakdown drift); store-clustered SEs; why staggered timing needs a different design. Then a synthetic control for one flagship store, with placebos and leave-one-out, and a comparison with DiD. Decision memo in margin, not sales</t>
+          <t>Favorita grocery panel with a planted rollout of an AI store assistant, adoption tied to the stores' real pre-trends; the April 2016 earthquake falls in the window. Before-after, 2x2 DiD and TWFE with store and period effects; an event study; what the pre-period can and cannot rule out (breakdown drift); store-clustered SEs; a small second wave and why staggered timing needs a different design. Then a synthetic control for one flagship store, with placebos and leave-one-out, and a comparison with DiD. Decision memo in margin, not sales</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Allowed, disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Assignments use real data that no lab touches. Each is graded on a complete, well-reasoned analysis pipeline, not on a performance score.</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1634,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -1822,7 +1826,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -2151,12 +2154,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>A2 and A3 ask the same question</t>
+          <t>A2 and A3 use different data</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Logs-trained policy scored next to the RCT-trained one on a locked evaluation set; needs an autograder.</t>
+          <t>Decided (10 Oct): A2 scores frozen policies on a locked Hillstrom holdout; A3 uses dunnhumby and is scored on a locked simulator. The RCT-versus-logs comparison on one locked set is dropped. The LLM-coded feature is in Lab 9, not A3.</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2227,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Lab 9 (cached LLM outputs, gold labels) and the A3 simulator of the coupon logs (built on the generator behind Lab 7) need the most up-front work.</t>
+          <t>The Houtan Coffee world (Labs 1 to 7, from 20 Oct), the Hillstrom file (A1, 22 Oct), Lab 9 (cached LLM outputs, gold labels), and the A3 locked simulator need the most up-front work.</t>
         </is>
       </c>
     </row>

--- a/plan/schedule.xlsx
+++ b/plan/schedule.xlsx
@@ -1085,7 +1085,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Labs 1 to 11 go with Meetings 1 to 11. Ten are graded, 1 point each; Lab 7 is optional and ungraded (its methods are graded in A3). Notebooks are expected soon after their meeting. AI roles: tool (Lab 2), decision-maker (Lab 5), analyst (Lab 7, optional), source of data (Lab 9), intervention (Lab 10). Each block of labs works in one semi-synthetic world with a planted truth: Labs 1 to 7 in Houtan Coffee's loyalty program (built on the Starbucks rewards data from Kaggle), Labs 8 and 9 in Airbnb listings and reviews (Inside Airbnb; the city is chosen later), Labs 10 and 11 in real store panels with planted rollouts. Notebooks describe their source data.</t>
+          <t>Labs 1 to 11 go with Meetings 1 to 11. Ten are graded, 1 point each; Lab 7 is optional and ungraded (its methods are graded in A3). Notebooks are expected soon after their meeting. AI roles: tool (Lab 2), decision-maker (Lab 5), analyst (Lab 7, optional), source of data (Lab 9), intervention (Lab 10). Each block of labs works in one semi-synthetic world with a planted truth: Labs 1 to 7 in Houtan Coffee's loyalty program (built on the Starbucks rewards data), Labs 8 and 9 in Airbnb listings and reviews, Labs 10 and 11 in real store panels with planted rollouts. Notebooks describe their source data.</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>

--- a/plan/schedule.xlsx
+++ b/plan/schedule.xlsx
@@ -536,6 +536,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -879,7 +880,7 @@
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Lab 8: DML on scanner data (in class)</t>
+          <t>Lab 8: DML on Airbnb listings (in class)</t>
         </is>
       </c>
       <c r="F11" s="6" t="n"/>

--- a/plan/schedule.xlsx
+++ b/plan/schedule.xlsx
@@ -536,7 +536,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -605,7 +604,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Lab 1: Python, probability and statistics review</t>
+          <t>Lab 1: Python, probability and statistics review; a potential-outcomes simulator that checks naive difference = ATT + selection bias</t>
         </is>
       </c>
       <c r="F4" s="4" t="n"/>
@@ -633,12 +632,12 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Experiments II: design. Fixing the plan in writing; power and MDE for a decision; CUPED; randomization unit, interference and clustered SEs; peeking and multiple metrics; to close, noncompliance in an RCT: ITT and first stage, compliance types, the LATE (potential outcomes; the draw as the instrument)</t>
+          <t>Experiments II: design. Fixing the plan in writing; power and MDE for a decision; CUPED; randomization unit, interference and clustered SEs; to close, noncompliance in an RCT: ITT and first stage, compliance types, the LATE (potential outcomes; the draw as the instrument)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Lab 2: A/B readout, then an LLM-generated readout checked by simulation tests</t>
+          <t>Lab 2: A/B readout by hand (SRM, robust SE, CUPED, test against the break-even); then an LLM-generated readout checked by simulation tests (planted-effect coverage, size under the null, the cost of peeking, multiple metrics)</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -678,12 +677,12 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>CATE II: models. S-, T-, X-learners; transformed outcome; DR- and R-learners; TARNet as a shared representation; choosing a model without ground truth (R-loss, DR pseudo-outcomes)</t>
+          <t>CATE II: models. S-, T-, X-learners; transformed outcome; DR- and R-learners with the known propensity of an RCT (double robustness waits for M6); TARNet as a shared representation; choosing a model without ground truth (R-loss, pseudo-outcomes)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Lab 3: meta-learners from scratch</t>
+          <t>Lab 3: meta-learners from scratch on three Houtan Coffee worlds with different planted effects; a provided TARNet notebook</t>
         </is>
       </c>
       <c r="F6" s="4" t="n"/>
@@ -714,20 +713,24 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>CATE III: causal trees. An estimand chosen by the data; causal trees that split on effect heterogeneity; the winner's curse; honesty and sample splitting; committing a discovery (discover, estimate, recommend)</t>
+          <t>CATE III: causal trees and forests. An estimand chosen by the data; causal trees that split on effect heterogeneity; the winner's curse; honesty and sample splitting; committing a discovery (discover, estimate, recommend); forests as adaptive neighbors and the forest estimate (link to the R-learner); CATE intervals and their limits</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>CATE IV: causal forests. Forests as adaptive neighbors; the forest estimate and local centering (link to the R-learner); CATE intervals and their limits; variable-importance pitfalls; BLP calibration test and GATES</t>
+          <t>CATE IV: evaluation. Testing for heterogeneity on held-out data (BLP calibration test, GATES); policy value and the policy-value identity; IPW value with the known propensity, and its variance; gain, profit and Qini curves; RATE; ranking vs calibration; selection vs evaluation data and freezing a policy; comparing two policies (paired SE)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Lab 4: causal forest on the coupon RCT</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
+          <t>Lab 4: causal forest with and without honesty across seeds; variable importance vs the calibration test; four targeting rules (one chosen by an LLM reading profiles) evaluated by IPW, Qini and RATE; isotonic recalibration</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>A1 (Fri 30 Oct)</t>
@@ -735,7 +738,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>Forest theory</t>
+          <t>Forest theory; evaluating prioritization rules</t>
         </is>
       </c>
       <c r="I7" s="6" t="n"/>
@@ -756,29 +759,21 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>CATE V: evaluation. Policy value and the policy-value identity; IPW value on held-out RCT data and its variance; gain, profit and Qini curves; RATE; ranking vs calibration, and isotonic recalibration; selection vs evaluation data; freezing a policy; comparing two policies (paired SE)</t>
+          <t>CATE V: allocation and decision. Net value per customer and break-even thresholds; customer-specific costs and the sure-thing cost; contact caps; budget as a knapsack and its shadow price; group constraints and the price of fairness; spending risk, noisy estimates and lower-bound allocation; capacity and the critical fractile; what the sum assumes (interference, support)</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Lab 5: CATE evaluation: four targeting rules (one chosen by an LLM) by IPW, Qini and RATE, isotonic recalibration, freeze then evaluate, paired comparison</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
+          <t>Lab 5: CATE allocation: greedy and LP allocation under a budget and caps; the shadow price; several coupon depths; lower-bound allocation; the price of a group constraint; allocations compared on held-out value with a paired comparison</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="inlineStr">
         <is>
           <t>Proposal (Sun 8 Nov)</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>Evaluating prioritization rules</t>
-        </is>
-      </c>
+      <c r="H8" s="8" t="n"/>
       <c r="I8" s="8" t="n"/>
     </row>
     <row r="9">
@@ -792,111 +787,111 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>CATE VI: allocation. Net value per customer and break-even thresholds; customer-specific costs and the sure-thing cost; contact caps; budget as a knapsack and its shadow price; several coupon depths; group constraints and the price of fairness; spending risk and the reserve; noisy estimates and lower-bound allocation; capacity and the critical fractile</t>
+          <t>Observational data I: identification and adjustment. Logs produced by a targeting rule; exchangeability, overlap, consistency; standardization (g-computation) and IPW with an estimated propensity; the balancing property; what regression adjustment estimates; good and bad controls (mediators, colliders, M-bias, post-treatment variables)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>CATE VII: policy learning. Predict-then-optimize, decision-focused learning and policy learning as one spectrum; empirical welfare maximization with DR scores; policy learning as weighted classification; policy trees; regret and policy-class complexity; deploying with holdouts; bandits as continuous experimentation; what the sum assumes (interference, support)</t>
+          <t>Observational data II: overlap, design and double robustness. Overlap diagnostics, trimming and the changed estimand; the outcome-free design stage; doubly robust AIPW (and why the M3 DR-learner works); the LaLonde benchmark; a first look at sensitivity to hidden confounding</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Lab 6: budgeted allocation and policy trees</t>
+          <t>Lab 6: observational data: logs built from the Houtan Coffee RCT by a known targeting rule; DAG and adjustment set; naive, regression, IPW, AIPW and matching against the RCT truth; overlap and trimming; then audit a tool-calling agent's analysis and add a guardrail</t>
         </is>
       </c>
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="6" t="n"/>
       <c r="H9" s="6" t="inlineStr">
         <is>
+          <t>Instrumental variables</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>H4 Instrumental variables</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Tue 10 Nov</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>DML I. The partially linear model; residualization (FWL) and what theta averages when effects vary; why plug-in ML fails (regularization and overfitting bias); cross-fitting; orthogonality in words; price elasticity</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>DML II. Overlap with a continuous treatment; the interactive model and AIPW scores; DML for CATE; inference with cross-fitting; omitted-variable sensitivity bounds and benchmarking</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Lab 7: DML from scratch on Airbnb listings: naive, fixed-effects and DML elasticities; hand-coded cross-fitting, then match a package; stability across nuisance learners and repeated splits; sensitivity bounds; the optimal price</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Regression discontinuity</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>H5 Regression discontinuity</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Thu 12 Nov</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>PROPOSAL PRESENTATIONS</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Policy learning from observational data. Predict-then-optimize, decision-focused learning and policy learning as one spectrum; cross-fitted DR scores from logs; empirical welfare maximization; policy learning as weighted classification; policy trees; regret and policy-class complexity; deploying with holdouts; bandits as continuous experimentation</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Lab 8: policy learning from the Houtan Coffee logs: cross-fitted DR scores; a depth-2 policy tree vs plug-in targeting; both evaluated on the RCT holdout</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>A2 (Sun 15 Nov)</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
           <t>Policy learning theory; dynamic regimes</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>H3 Sequential decisions</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>Tue 10 Nov</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Observational data I: identification and adjustment. Logs produced by a targeting rule; exchangeability, overlap, consistency; standardization (g-computation) and IPW; the balancing property; what regression adjustment estimates; good and bad controls (mediators, colliders, M-bias, post-treatment variables)</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>Observational data II: overlap, design and double robustness. Overlap diagnostics, trimming and the changed estimand; the outcome-free design stage; doubly robust AIPW; the LaLonde benchmark; a first look at sensitivity to hidden confounding</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>PROPOSAL PRESENTATIONS. Lab 7 (optional, ungraded, take-home): observational methods on logs built from an RCT, then an agent's analysis audited</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>Instrumental variables</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>H4 Instrumental variables</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Thu 12 Nov</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>DML I. The partially linear model; residualization (FWL) and what theta averages when effects vary; why plug-in ML fails (regularization and overfitting bias); cross-fitting; orthogonality in words; price elasticity</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>DML II. Inference and repeated splits; choice of nuisance learners; overlap with a continuous treatment; the interactive model and AIPW scores; DML for CATE; omitted-variable sensitivity bounds and benchmarking</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Lab 8: DML on Airbnb listings (in class)</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>A2 (Sun 15 Nov)</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Regression discontinuity</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>H5 Regression discontinuity</t>
         </is>
       </c>
     </row>
